--- a/calendar_chilean_2022B.xlsx
+++ b/calendar_chilean_2022B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed268546/Dropbox/Mac/Documents/codes/SPOCK_chilean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADB8223-AA32-6D45-83DA-798BE28C6187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE748142-E555-1345-B5FB-C6AA9566E668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="900" windowWidth="35840" windowHeight="21100" xr2:uid="{29A8BF1E-0110-C24B-9407-C010B9269ACA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21100" xr2:uid="{29A8BF1E-0110-C24B-9407-C010B9269ACA}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="29">
   <si>
     <t>Date</t>
   </si>
@@ -117,6 +116,12 @@
   </si>
   <si>
     <t>CN2022B-31</t>
+  </si>
+  <si>
+    <t>techncal</t>
+  </si>
+  <si>
+    <t>technical</t>
   </si>
 </sst>
 </file>
@@ -567,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -690,25 +695,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1086,7 +1085,7 @@
       <c r="F2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="46" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="44" t="s">
@@ -1118,13 +1117,13 @@
       <c r="F3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="50" t="s">
+      <c r="H3" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="42" t="s">
@@ -1150,13 +1149,13 @@
       <c r="F4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="50" t="s">
+      <c r="H4" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J4" s="42" t="s">
@@ -1180,9 +1179,9 @@
         <v>0</v>
       </c>
       <c r="F5" s="15"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
       <c r="J5" s="16"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1202,9 +1201,9 @@
         <v>0</v>
       </c>
       <c r="F6" s="15"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
       <c r="J6" s="16"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1224,9 +1223,9 @@
         <v>0</v>
       </c>
       <c r="F7" s="15"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
       <c r="J7" s="16"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1246,9 +1245,9 @@
         <v>0</v>
       </c>
       <c r="F8" s="15"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
       <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1270,13 +1269,13 @@
       <c r="F9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="49" t="s">
+      <c r="G9" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="50" t="s">
+      <c r="H9" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="42" t="s">
@@ -1302,13 +1301,13 @@
       <c r="F10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="50" t="s">
+      <c r="H10" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="42" t="s">
@@ -1334,13 +1333,13 @@
       <c r="F11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="49" t="s">
+      <c r="G11" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="50" t="s">
+      <c r="H11" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="42" t="s">
@@ -1364,9 +1363,9 @@
         <v>0</v>
       </c>
       <c r="F12" s="40"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
       <c r="J12" s="31"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1386,9 +1385,9 @@
         <v>0</v>
       </c>
       <c r="F13" s="15"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
       <c r="J13" s="31"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1408,9 +1407,9 @@
         <v>0</v>
       </c>
       <c r="F14" s="40"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
       <c r="J14" s="31"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1430,9 +1429,9 @@
         <v>0</v>
       </c>
       <c r="F15" s="15"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
       <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1454,20 +1453,20 @@
       <c r="F16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="49" t="s">
+      <c r="G16" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="50" t="s">
+      <c r="H16" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J16" s="43" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>44881</v>
       </c>
@@ -1486,20 +1485,20 @@
       <c r="F17" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="49" t="s">
+      <c r="G17" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="50" t="s">
+      <c r="H17" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="43" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>44882</v>
       </c>
@@ -1518,20 +1517,20 @@
       <c r="F18" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="49" t="s">
+      <c r="G18" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="50" t="s">
+      <c r="H18" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J18" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>44883</v>
       </c>
@@ -1548,12 +1547,12 @@
         <v>0</v>
       </c>
       <c r="F19" s="15"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>44884</v>
       </c>
@@ -1570,12 +1569,12 @@
         <v>0</v>
       </c>
       <c r="F20" s="15"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
       <c r="J20" s="31"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>44885</v>
       </c>
@@ -1592,12 +1591,12 @@
         <v>0</v>
       </c>
       <c r="F21" s="40"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
       <c r="J21" s="31"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>44886</v>
       </c>
@@ -1614,12 +1613,12 @@
         <v>0</v>
       </c>
       <c r="F22" s="40"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
       <c r="J22" s="31"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>44887</v>
       </c>
@@ -1638,20 +1637,20 @@
       <c r="F23" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="49" t="s">
+      <c r="G23" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="51" t="s">
+      <c r="H23" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J23" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>44888</v>
       </c>
@@ -1670,20 +1669,23 @@
       <c r="F24" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G24" s="49" t="s">
+      <c r="G24" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="51" t="s">
+      <c r="H24" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J24" s="43" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>44889</v>
       </c>
@@ -1702,20 +1704,20 @@
       <c r="F25" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="49" t="s">
+      <c r="G25" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H25" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" s="51" t="s">
+      <c r="H25" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J25" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>44890</v>
       </c>
@@ -1732,12 +1734,12 @@
         <v>0</v>
       </c>
       <c r="F26" s="15"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
       <c r="J26" s="16"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>44891</v>
       </c>
@@ -1754,12 +1756,12 @@
         <v>0</v>
       </c>
       <c r="F27" s="15"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
       <c r="J27" s="16"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>44892</v>
       </c>
@@ -1776,12 +1778,12 @@
         <v>0</v>
       </c>
       <c r="F28" s="15"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
       <c r="J28" s="16"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>44893</v>
       </c>
@@ -1798,12 +1800,12 @@
         <v>0</v>
       </c>
       <c r="F29" s="15"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
       <c r="J29" s="31"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>44894</v>
       </c>
@@ -1822,20 +1824,20 @@
       <c r="F30" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="49" t="s">
+      <c r="G30" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H30" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="51" t="s">
+      <c r="H30" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J30" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>44895</v>
       </c>
@@ -1854,20 +1856,20 @@
       <c r="F31" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H31" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" s="51" t="s">
+      <c r="H31" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J31" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>44896</v>
       </c>
@@ -1886,13 +1888,13 @@
       <c r="F32" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G32" s="49" t="s">
+      <c r="G32" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" s="51" t="s">
+      <c r="H32" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J32" s="42" t="s">
@@ -1916,9 +1918,9 @@
         <v>0</v>
       </c>
       <c r="F33" s="15"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
       <c r="J33" s="16"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1938,9 +1940,9 @@
         <v>0</v>
       </c>
       <c r="F34" s="15"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
       <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -1960,9 +1962,9 @@
         <v>0</v>
       </c>
       <c r="F35" s="15"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
       <c r="J35" s="16"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1982,9 +1984,9 @@
         <v>0</v>
       </c>
       <c r="F36" s="15"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
       <c r="J36" s="16"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -2006,13 +2008,13 @@
       <c r="F37" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="50" t="s">
+      <c r="H37" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="42" t="s">
@@ -2038,13 +2040,13 @@
       <c r="F38" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="49" t="s">
+      <c r="G38" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="50" t="s">
+      <c r="H38" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J38" s="42" t="s">
@@ -2070,13 +2072,13 @@
       <c r="F39" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G39" s="49" t="s">
+      <c r="G39" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" s="50" t="s">
+      <c r="H39" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="42" t="s">
@@ -2100,9 +2102,9 @@
         <v>0</v>
       </c>
       <c r="F40" s="15"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="46"/>
-      <c r="I40" s="46"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
       <c r="J40" s="31"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -2122,9 +2124,9 @@
         <v>0</v>
       </c>
       <c r="F41" s="15"/>
-      <c r="G41" s="46"/>
-      <c r="H41" s="46"/>
-      <c r="I41" s="46"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
       <c r="J41" s="16"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -2144,9 +2146,9 @@
         <v>0</v>
       </c>
       <c r="F42" s="15"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="46"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
       <c r="J42" s="16"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -2166,9 +2168,9 @@
         <v>0</v>
       </c>
       <c r="F43" s="15"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="46"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
       <c r="J43" s="16"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -2190,13 +2192,13 @@
       <c r="F44" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="49" t="s">
+      <c r="G44" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H44" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" s="51" t="s">
+      <c r="H44" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J44" s="42" t="s">
@@ -2222,13 +2224,13 @@
       <c r="F45" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G45" s="49" t="s">
+      <c r="G45" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I45" s="51" t="s">
+      <c r="H45" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J45" s="43" t="s">
@@ -2254,13 +2256,13 @@
       <c r="F46" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G46" s="49" t="s">
+      <c r="G46" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I46" s="51" t="s">
+      <c r="H46" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="42" t="s">
@@ -2284,9 +2286,9 @@
         <v>0</v>
       </c>
       <c r="F47" s="15"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
       <c r="J47" s="31"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -2306,9 +2308,9 @@
         <v>0</v>
       </c>
       <c r="F48" s="15"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="47"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="20"/>
       <c r="J48" s="31"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
@@ -2328,9 +2330,9 @@
         <v>0</v>
       </c>
       <c r="F49" s="15"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
       <c r="J49" s="31"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
@@ -2350,9 +2352,9 @@
         <v>0</v>
       </c>
       <c r="F50" s="15"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
       <c r="J50" s="16"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2374,13 +2376,13 @@
       <c r="F51" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G51" s="49" t="s">
+      <c r="G51" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H51" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" s="51" t="s">
+      <c r="H51" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="42" t="s">
@@ -2406,13 +2408,13 @@
       <c r="F52" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G52" s="49" t="s">
+      <c r="G52" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I52" s="51" t="s">
+      <c r="H52" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J52" s="42" t="s">
@@ -2438,13 +2440,13 @@
       <c r="F53" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G53" s="49" t="s">
+      <c r="G53" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I53" s="51" t="s">
+      <c r="H53" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J53" s="42" t="s">
@@ -2468,9 +2470,9 @@
         <v>0</v>
       </c>
       <c r="F54" s="15"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
       <c r="J54" s="16"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
@@ -2490,9 +2492,9 @@
         <v>0</v>
       </c>
       <c r="F55" s="15"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
       <c r="J55" s="16"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
@@ -2512,9 +2514,9 @@
         <v>0</v>
       </c>
       <c r="F56" s="15"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
       <c r="J56" s="31"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
@@ -2534,9 +2536,9 @@
         <v>0</v>
       </c>
       <c r="F57" s="15"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="46"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
       <c r="J57" s="31"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
@@ -2558,13 +2560,13 @@
       <c r="F58" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="49" t="s">
+      <c r="G58" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H58" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I58" s="51" t="s">
+      <c r="H58" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J58" s="43" t="s">
@@ -2590,13 +2592,13 @@
       <c r="F59" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G59" s="49" t="s">
+      <c r="G59" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H59" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" s="51" t="s">
+      <c r="H59" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="43" t="s">
@@ -2622,13 +2624,13 @@
       <c r="F60" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G60" s="49" t="s">
+      <c r="G60" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H60" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" s="51" t="s">
+      <c r="H60" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="49" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="43" t="s">
@@ -2652,9 +2654,9 @@
         <v>0</v>
       </c>
       <c r="F61" s="15"/>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
       <c r="J61" s="16"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
@@ -2674,9 +2676,9 @@
         <v>0</v>
       </c>
       <c r="F62" s="15"/>
-      <c r="G62" s="46"/>
-      <c r="H62" s="46"/>
-      <c r="I62" s="46"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
       <c r="J62" s="16"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
@@ -2696,9 +2698,9 @@
         <v>0</v>
       </c>
       <c r="F63" s="15"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="46"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
       <c r="J63" s="16"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
@@ -2718,9 +2720,9 @@
         <v>0</v>
       </c>
       <c r="F64" s="15"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="46"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
       <c r="J64" s="16"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
@@ -2742,13 +2744,13 @@
       <c r="F65" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G65" s="49" t="s">
+      <c r="G65" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H65" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I65" s="50" t="s">
+      <c r="H65" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="42" t="s">
@@ -2774,13 +2776,13 @@
       <c r="F66" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G66" s="49" t="s">
+      <c r="G66" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H66" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" s="50" t="s">
+      <c r="H66" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J66" s="42" t="s">
@@ -2806,13 +2808,13 @@
       <c r="F67" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G67" s="49" t="s">
+      <c r="G67" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H67" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="50" t="s">
+      <c r="H67" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J67" s="42" t="s">
@@ -2836,9 +2838,9 @@
         <v>0</v>
       </c>
       <c r="F68" s="15"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
       <c r="J68" s="16"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
@@ -2858,9 +2860,9 @@
         <v>0</v>
       </c>
       <c r="F69" s="15"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="46"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
       <c r="J69" s="16"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
@@ -2880,9 +2882,9 @@
         <v>0</v>
       </c>
       <c r="F70" s="15"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
       <c r="J70" s="16"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
@@ -2902,9 +2904,9 @@
         <v>0</v>
       </c>
       <c r="F71" s="15"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
       <c r="J71" s="16"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
@@ -2926,13 +2928,13 @@
       <c r="F72" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="49" t="s">
+      <c r="G72" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H72" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I72" s="50" t="s">
+      <c r="H72" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J72" s="42" t="s">
@@ -2958,13 +2960,13 @@
       <c r="F73" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G73" s="49" t="s">
+      <c r="G73" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H73" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I73" s="50" t="s">
+      <c r="H73" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J73" s="42" t="s">
@@ -2990,13 +2992,13 @@
       <c r="F74" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G74" s="49" t="s">
+      <c r="G74" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H74" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I74" s="50" t="s">
+      <c r="H74" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J74" s="42" t="s">
@@ -3020,9 +3022,9 @@
         <v>0</v>
       </c>
       <c r="F75" s="15"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
       <c r="J75" s="31"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
@@ -3042,9 +3044,9 @@
         <v>0</v>
       </c>
       <c r="F76" s="15"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
       <c r="J76" s="31"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
@@ -3064,9 +3066,9 @@
         <v>0</v>
       </c>
       <c r="F77" s="15"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="46"/>
-      <c r="I77" s="46"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
       <c r="J77" s="16"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
@@ -3086,9 +3088,9 @@
         <v>0</v>
       </c>
       <c r="F78" s="15"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46"/>
-      <c r="I78" s="46"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
       <c r="J78" s="16"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
@@ -3110,13 +3112,13 @@
       <c r="F79" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G79" s="49" t="s">
+      <c r="G79" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H79" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I79" s="50" t="s">
+      <c r="H79" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="42" t="s">
@@ -3142,13 +3144,13 @@
       <c r="F80" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G80" s="49" t="s">
+      <c r="G80" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H80" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I80" s="50" t="s">
+      <c r="H80" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J80" s="42" t="s">
@@ -3174,13 +3176,13 @@
       <c r="F81" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G81" s="49" t="s">
+      <c r="G81" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H81" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I81" s="50" t="s">
+      <c r="H81" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J81" s="42" t="s">
@@ -3204,9 +3206,9 @@
         <v>0</v>
       </c>
       <c r="F82" s="15"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="46"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
       <c r="J82" s="16"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
@@ -3226,9 +3228,9 @@
         <v>0</v>
       </c>
       <c r="F83" s="15"/>
-      <c r="G83" s="46"/>
-      <c r="H83" s="46"/>
-      <c r="I83" s="46"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
       <c r="J83" s="31"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
@@ -3248,9 +3250,9 @@
         <v>0</v>
       </c>
       <c r="F84" s="15"/>
-      <c r="G84" s="46"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="46"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
       <c r="J84" s="31"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
@@ -3270,9 +3272,9 @@
         <v>0</v>
       </c>
       <c r="F85" s="15"/>
-      <c r="G85" s="46"/>
-      <c r="H85" s="46"/>
-      <c r="I85" s="46"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
       <c r="J85" s="31"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
@@ -3294,13 +3296,13 @@
       <c r="F86" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="49" t="s">
+      <c r="G86" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H86" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I86" s="50" t="s">
+      <c r="H86" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J86" s="42" t="s">
@@ -3326,13 +3328,13 @@
       <c r="F87" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G87" s="49" t="s">
+      <c r="G87" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H87" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I87" s="50" t="s">
+      <c r="H87" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J87" s="42" t="s">
@@ -3358,13 +3360,13 @@
       <c r="F88" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G88" s="49" t="s">
+      <c r="G88" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H88" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I88" s="50" t="s">
+      <c r="H88" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J88" s="42" t="s">
@@ -3388,9 +3390,9 @@
         <v>0</v>
       </c>
       <c r="F89" s="15"/>
-      <c r="G89" s="46"/>
-      <c r="H89" s="46"/>
-      <c r="I89" s="46"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
       <c r="J89" s="16"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
@@ -3410,9 +3412,9 @@
         <v>0</v>
       </c>
       <c r="F90" s="15"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7"/>
       <c r="J90" s="16"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
@@ -3432,9 +3434,9 @@
         <v>0</v>
       </c>
       <c r="F91" s="15"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="46"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
       <c r="J91" s="16"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
@@ -3454,9 +3456,9 @@
         <v>0</v>
       </c>
       <c r="F92" s="15"/>
-      <c r="G92" s="46"/>
-      <c r="H92" s="46"/>
-      <c r="I92" s="47"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="20"/>
       <c r="J92" s="16"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
@@ -3478,11 +3480,11 @@
       <c r="F93" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G93" s="46"/>
-      <c r="H93" s="52" t="s">
+      <c r="G93" s="7"/>
+      <c r="H93" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I93" s="52" t="s">
+      <c r="I93" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J93" s="45" t="s">
@@ -3508,11 +3510,11 @@
       <c r="F94" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G94" s="46"/>
-      <c r="H94" s="52" t="s">
+      <c r="G94" s="7"/>
+      <c r="H94" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I94" s="52" t="s">
+      <c r="I94" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J94" s="45" t="s">
@@ -3538,11 +3540,11 @@
       <c r="F95" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G95" s="46"/>
-      <c r="H95" s="52" t="s">
+      <c r="G95" s="7"/>
+      <c r="H95" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I95" s="52" t="s">
+      <c r="I95" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J95" s="45" t="s">
@@ -3566,9 +3568,9 @@
         <v>0</v>
       </c>
       <c r="F96" s="15"/>
-      <c r="G96" s="46"/>
-      <c r="H96" s="46"/>
-      <c r="I96" s="46"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
       <c r="J96" s="16"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
@@ -3588,9 +3590,9 @@
         <v>0</v>
       </c>
       <c r="F97" s="15"/>
-      <c r="G97" s="46"/>
-      <c r="H97" s="46"/>
-      <c r="I97" s="46"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7"/>
       <c r="J97" s="16"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
@@ -3610,9 +3612,9 @@
         <v>0</v>
       </c>
       <c r="F98" s="15"/>
-      <c r="G98" s="46"/>
-      <c r="H98" s="46"/>
-      <c r="I98" s="46"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7"/>
       <c r="J98" s="16"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
@@ -3632,9 +3634,9 @@
         <v>0</v>
       </c>
       <c r="F99" s="15"/>
-      <c r="G99" s="46"/>
-      <c r="H99" s="46"/>
-      <c r="I99" s="46"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7"/>
       <c r="J99" s="16"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
@@ -3656,11 +3658,11 @@
       <c r="F100" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G100" s="46"/>
-      <c r="H100" s="52" t="s">
+      <c r="G100" s="7"/>
+      <c r="H100" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I100" s="52" t="s">
+      <c r="I100" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J100" s="45" t="s">
@@ -3686,11 +3688,11 @@
       <c r="F101" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G101" s="46"/>
-      <c r="H101" s="52" t="s">
+      <c r="G101" s="7"/>
+      <c r="H101" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I101" s="52" t="s">
+      <c r="I101" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J101" s="45" t="s">
@@ -3716,11 +3718,11 @@
       <c r="F102" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G102" s="46"/>
-      <c r="H102" s="52" t="s">
+      <c r="G102" s="7"/>
+      <c r="H102" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I102" s="52" t="s">
+      <c r="I102" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J102" s="45" t="s">
@@ -3744,9 +3746,9 @@
         <v>0</v>
       </c>
       <c r="F103" s="15"/>
-      <c r="G103" s="46"/>
-      <c r="H103" s="46"/>
-      <c r="I103" s="47"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="20"/>
       <c r="J103" s="16"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
@@ -3766,9 +3768,9 @@
         <v>0</v>
       </c>
       <c r="F104" s="15"/>
-      <c r="G104" s="46"/>
-      <c r="H104" s="46"/>
-      <c r="I104" s="46"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
       <c r="J104" s="16"/>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
@@ -3788,9 +3790,9 @@
         <v>0</v>
       </c>
       <c r="F105" s="15"/>
-      <c r="G105" s="46"/>
-      <c r="H105" s="46"/>
-      <c r="I105" s="46"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
       <c r="J105" s="16"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
@@ -3810,9 +3812,9 @@
         <v>0</v>
       </c>
       <c r="F106" s="15"/>
-      <c r="G106" s="46"/>
-      <c r="H106" s="46"/>
-      <c r="I106" s="46"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="7"/>
       <c r="J106" s="16"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -3834,13 +3836,13 @@
       <c r="F107" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G107" s="49" t="s">
+      <c r="G107" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H107" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I107" s="50" t="s">
+      <c r="H107" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J107" s="42" t="s">
@@ -3866,13 +3868,13 @@
       <c r="F108" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G108" s="49" t="s">
+      <c r="G108" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H108" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I108" s="50" t="s">
+      <c r="H108" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I108" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J108" s="42" t="s">
@@ -3898,13 +3900,13 @@
       <c r="F109" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G109" s="49" t="s">
+      <c r="G109" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H109" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I109" s="50" t="s">
+      <c r="H109" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J109" s="43" t="s">
@@ -3928,9 +3930,9 @@
         <v>0</v>
       </c>
       <c r="F110" s="15"/>
-      <c r="G110" s="46"/>
-      <c r="H110" s="46"/>
-      <c r="I110" s="47"/>
+      <c r="G110" s="7"/>
+      <c r="H110" s="7"/>
+      <c r="I110" s="20"/>
       <c r="J110" s="16"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
@@ -3950,9 +3952,9 @@
         <v>0</v>
       </c>
       <c r="F111" s="15"/>
-      <c r="G111" s="46"/>
-      <c r="H111" s="46"/>
-      <c r="I111" s="47"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="20"/>
       <c r="J111" s="16"/>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
@@ -3972,12 +3974,12 @@
         <v>0</v>
       </c>
       <c r="F112" s="15"/>
-      <c r="G112" s="46"/>
-      <c r="H112" s="46"/>
-      <c r="I112" s="47"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="20"/>
       <c r="J112" s="16"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="9">
         <v>44977</v>
       </c>
@@ -3994,12 +3996,12 @@
         <v>0</v>
       </c>
       <c r="F113" s="15"/>
-      <c r="G113" s="46"/>
-      <c r="H113" s="46"/>
-      <c r="I113" s="46"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
       <c r="J113" s="16"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="9">
         <v>44978</v>
       </c>
@@ -4018,20 +4020,20 @@
       <c r="F114" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G114" s="49" t="s">
+      <c r="G114" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H114" s="50" t="s">
+      <c r="H114" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I114" s="50" t="s">
+      <c r="I114" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J114" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="9">
         <v>44979</v>
       </c>
@@ -4050,20 +4052,20 @@
       <c r="F115" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G115" s="49" t="s">
+      <c r="G115" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H115" s="50" t="s">
+      <c r="H115" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I115" s="50" t="s">
+      <c r="I115" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J115" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="9">
         <v>44980</v>
       </c>
@@ -4082,20 +4084,20 @@
       <c r="F116" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G116" s="49" t="s">
+      <c r="G116" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H116" s="50" t="s">
+      <c r="H116" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I116" s="50" t="s">
+      <c r="I116" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J116" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="9">
         <v>44981</v>
       </c>
@@ -4112,12 +4114,12 @@
         <v>0</v>
       </c>
       <c r="F117" s="15"/>
-      <c r="G117" s="46"/>
-      <c r="H117" s="46"/>
-      <c r="I117" s="46"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="7"/>
       <c r="J117" s="16"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="9">
         <v>44982</v>
       </c>
@@ -4134,12 +4136,12 @@
         <v>0</v>
       </c>
       <c r="F118" s="15"/>
-      <c r="G118" s="46"/>
-      <c r="H118" s="46"/>
-      <c r="I118" s="46"/>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7"/>
       <c r="J118" s="16"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="9">
         <v>44983</v>
       </c>
@@ -4156,12 +4158,12 @@
         <v>0</v>
       </c>
       <c r="F119" s="15"/>
-      <c r="G119" s="46"/>
-      <c r="H119" s="46"/>
-      <c r="I119" s="46"/>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7"/>
       <c r="J119" s="16"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="9">
         <v>44984</v>
       </c>
@@ -4178,12 +4180,12 @@
         <v>0</v>
       </c>
       <c r="F120" s="40"/>
-      <c r="G120" s="47"/>
-      <c r="H120" s="46"/>
-      <c r="I120" s="46"/>
+      <c r="G120" s="20"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="7"/>
       <c r="J120" s="16"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="9">
         <v>44985</v>
       </c>
@@ -4202,20 +4204,20 @@
       <c r="F121" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G121" s="49" t="s">
+      <c r="G121" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H121" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I121" s="50" t="s">
+      <c r="H121" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I121" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J121" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="9">
         <v>44986</v>
       </c>
@@ -4234,20 +4236,20 @@
       <c r="F122" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G122" s="49" t="s">
+      <c r="G122" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H122" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I122" s="50" t="s">
+      <c r="H122" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I122" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J122" s="42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="9">
         <v>44987</v>
       </c>
@@ -4266,20 +4268,23 @@
       <c r="F123" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G123" s="49" t="s">
+      <c r="G123" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H123" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I123" s="50" t="s">
+      <c r="H123" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I123" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J123" s="43" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K123" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="9">
         <v>44988</v>
       </c>
@@ -4296,12 +4301,12 @@
         <v>0</v>
       </c>
       <c r="F124" s="15"/>
-      <c r="G124" s="46"/>
-      <c r="H124" s="46"/>
-      <c r="I124" s="46"/>
+      <c r="G124" s="7"/>
+      <c r="H124" s="7"/>
+      <c r="I124" s="7"/>
       <c r="J124" s="16"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="9">
         <v>44989</v>
       </c>
@@ -4318,12 +4323,12 @@
         <v>0</v>
       </c>
       <c r="F125" s="15"/>
-      <c r="G125" s="46"/>
-      <c r="H125" s="46"/>
-      <c r="I125" s="46"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
+      <c r="I125" s="7"/>
       <c r="J125" s="16"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="9">
         <v>44990</v>
       </c>
@@ -4340,12 +4345,12 @@
         <v>0</v>
       </c>
       <c r="F126" s="15"/>
-      <c r="G126" s="46"/>
-      <c r="H126" s="46"/>
-      <c r="I126" s="46"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="7"/>
       <c r="J126" s="16"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="9">
         <v>44991</v>
       </c>
@@ -4362,12 +4367,12 @@
         <v>0</v>
       </c>
       <c r="F127" s="15"/>
-      <c r="G127" s="46"/>
-      <c r="H127" s="46"/>
-      <c r="I127" s="46"/>
+      <c r="G127" s="7"/>
+      <c r="H127" s="7"/>
+      <c r="I127" s="7"/>
       <c r="J127" s="16"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="9">
         <v>44992</v>
       </c>
@@ -4386,11 +4391,11 @@
       <c r="F128" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G128" s="46"/>
-      <c r="H128" s="52" t="s">
+      <c r="G128" s="7"/>
+      <c r="H128" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I128" s="52" t="s">
+      <c r="I128" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J128" s="45" t="s">
@@ -4416,11 +4421,11 @@
       <c r="F129" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G129" s="46"/>
-      <c r="H129" s="52" t="s">
+      <c r="G129" s="7"/>
+      <c r="H129" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I129" s="52" t="s">
+      <c r="I129" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J129" s="45" t="s">
@@ -4446,11 +4451,11 @@
       <c r="F130" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G130" s="46"/>
-      <c r="H130" s="52" t="s">
+      <c r="G130" s="7"/>
+      <c r="H130" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I130" s="52" t="s">
+      <c r="I130" s="50" t="s">
         <v>12</v>
       </c>
       <c r="J130" s="45" t="s">
@@ -4474,9 +4479,9 @@
         <v>0</v>
       </c>
       <c r="F131" s="15"/>
-      <c r="G131" s="46"/>
-      <c r="H131" s="46"/>
-      <c r="I131" s="46"/>
+      <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
+      <c r="I131" s="7"/>
       <c r="J131" s="16"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
@@ -4496,9 +4501,9 @@
         <v>0</v>
       </c>
       <c r="F132" s="15"/>
-      <c r="G132" s="46"/>
-      <c r="H132" s="46"/>
-      <c r="I132" s="46"/>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="7"/>
       <c r="J132" s="16"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
@@ -4518,9 +4523,9 @@
         <v>0</v>
       </c>
       <c r="F133" s="15"/>
-      <c r="G133" s="46"/>
-      <c r="H133" s="46"/>
-      <c r="I133" s="46"/>
+      <c r="G133" s="7"/>
+      <c r="H133" s="7"/>
+      <c r="I133" s="7"/>
       <c r="J133" s="16"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
@@ -4540,9 +4545,9 @@
         <v>0</v>
       </c>
       <c r="F134" s="15"/>
-      <c r="G134" s="46"/>
-      <c r="H134" s="46"/>
-      <c r="I134" s="46"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="7"/>
       <c r="J134" s="16"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
@@ -4564,13 +4569,13 @@
       <c r="F135" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G135" s="49" t="s">
+      <c r="G135" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H135" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I135" s="50" t="s">
+      <c r="H135" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I135" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J135" s="42" t="s">
@@ -4596,13 +4601,13 @@
       <c r="F136" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G136" s="49" t="s">
+      <c r="G136" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H136" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I136" s="50" t="s">
+      <c r="H136" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I136" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J136" s="42" t="s">
@@ -4628,13 +4633,13 @@
       <c r="F137" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G137" s="49" t="s">
+      <c r="G137" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H137" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I137" s="50" t="s">
+      <c r="H137" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I137" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J137" s="42" t="s">
@@ -4658,9 +4663,9 @@
         <v>0</v>
       </c>
       <c r="F138" s="40"/>
-      <c r="G138" s="47"/>
-      <c r="H138" s="46"/>
-      <c r="I138" s="46"/>
+      <c r="G138" s="20"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="7"/>
       <c r="J138" s="16"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -4680,9 +4685,9 @@
         <v>0</v>
       </c>
       <c r="F139" s="15"/>
-      <c r="G139" s="46"/>
-      <c r="H139" s="47"/>
-      <c r="I139" s="47"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="20"/>
+      <c r="I139" s="20"/>
       <c r="J139" s="16"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
@@ -4702,9 +4707,9 @@
         <v>0</v>
       </c>
       <c r="F140" s="15"/>
-      <c r="G140" s="46"/>
-      <c r="H140" s="46"/>
-      <c r="I140" s="46"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
+      <c r="I140" s="7"/>
       <c r="J140" s="16"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
@@ -4724,9 +4729,9 @@
         <v>0</v>
       </c>
       <c r="F141" s="15"/>
-      <c r="G141" s="46"/>
-      <c r="H141" s="46"/>
-      <c r="I141" s="46"/>
+      <c r="G141" s="7"/>
+      <c r="H141" s="7"/>
+      <c r="I141" s="7"/>
       <c r="J141" s="16"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
@@ -4748,13 +4753,13 @@
       <c r="F142" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G142" s="49" t="s">
+      <c r="G142" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H142" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I142" s="50" t="s">
+      <c r="H142" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I142" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J142" s="42" t="s">
@@ -4780,13 +4785,13 @@
       <c r="F143" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G143" s="49" t="s">
+      <c r="G143" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H143" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I143" s="50" t="s">
+      <c r="H143" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I143" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J143" s="42" t="s">
@@ -4812,13 +4817,13 @@
       <c r="F144" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G144" s="49" t="s">
+      <c r="G144" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H144" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I144" s="50" t="s">
+      <c r="H144" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I144" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J144" s="42" t="s">
@@ -4842,9 +4847,9 @@
         <v>0</v>
       </c>
       <c r="F145" s="15"/>
-      <c r="G145" s="46"/>
-      <c r="H145" s="46"/>
-      <c r="I145" s="46"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
+      <c r="I145" s="7"/>
       <c r="J145" s="16"/>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.2">
@@ -4864,9 +4869,9 @@
         <v>0</v>
       </c>
       <c r="F146" s="15"/>
-      <c r="G146" s="46"/>
-      <c r="H146" s="46"/>
-      <c r="I146" s="47"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+      <c r="I146" s="20"/>
       <c r="J146" s="16"/>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.2">
@@ -4886,9 +4891,9 @@
         <v>0</v>
       </c>
       <c r="F147" s="40"/>
-      <c r="G147" s="47"/>
-      <c r="H147" s="47"/>
-      <c r="I147" s="47"/>
+      <c r="G147" s="20"/>
+      <c r="H147" s="20"/>
+      <c r="I147" s="20"/>
       <c r="J147" s="16"/>
     </row>
     <row r="148" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4908,9 +4913,9 @@
         <v>0</v>
       </c>
       <c r="F148" s="40"/>
-      <c r="G148" s="47"/>
-      <c r="H148" s="47"/>
-      <c r="I148" s="47"/>
+      <c r="G148" s="20"/>
+      <c r="H148" s="20"/>
+      <c r="I148" s="20"/>
       <c r="J148" s="16"/>
     </row>
     <row r="149" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -4930,9 +4935,9 @@
         <v>0</v>
       </c>
       <c r="F149" s="15"/>
-      <c r="G149" s="46"/>
-      <c r="H149" s="46"/>
-      <c r="I149" s="46"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+      <c r="I149" s="7"/>
       <c r="J149" s="16"/>
       <c r="L149" s="27" t="s">
         <v>17</v>
@@ -4961,13 +4966,13 @@
       <c r="F150" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G150" s="49" t="s">
+      <c r="G150" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H150" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I150" s="50" t="s">
+      <c r="H150" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I150" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J150" s="42" t="s">
@@ -5000,13 +5005,13 @@
       <c r="F151" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G151" s="49" t="s">
+      <c r="G151" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H151" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I151" s="50" t="s">
+      <c r="H151" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I151" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J151" s="42" t="s">
@@ -5039,13 +5044,13 @@
       <c r="F152" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G152" s="49" t="s">
+      <c r="G152" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H152" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I152" s="50" t="s">
+      <c r="H152" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I152" s="48" t="s">
         <v>18</v>
       </c>
       <c r="J152" s="42" t="s">
